--- a/data/dados/TRT/data.XLSX
+++ b/data/dados/TRT/data.XLSX
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8263" uniqueCount="3446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8323" uniqueCount="3446">
   <si>
     <t xml:space="preserve">Número da Questão</t>
   </si>
@@ -15241,7 +15241,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -15251,6 +15251,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -19539,3521 +19543,3700 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y1048576"/>
+  <dimension ref="A1:Y61"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="1" width="9.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="23.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="9" style="1" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="9" style="0" width="9.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="0" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>652</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="0" t="s">
         <v>658</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="P2" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="0" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>664</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="P3" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q3" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="S3" s="0" t="s">
         <v>671</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="T3" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" s="0" t="s">
         <v>672</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>673</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="P4" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q4" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4" s="0" t="s">
         <v>679</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" s="0" t="s">
         <v>680</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="T4" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="U4" s="0" t="s">
         <v>681</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="V4" s="0" t="s">
         <v>682</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="W4" s="0" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>683</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="0" t="s">
         <v>685</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="0" t="s">
         <v>686</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="0" t="s">
         <v>687</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="0" t="s">
         <v>688</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="0" t="s">
         <v>689</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="P5" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q5" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="S5" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="T5" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="U5" s="0" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>691</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="P6" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q6" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="R6" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="S6" s="0" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>698</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="0" t="s">
         <v>700</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="0" t="s">
         <v>701</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="0" t="s">
         <v>702</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="0" t="s">
         <v>703</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="O7" s="0" t="s">
         <v>557</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="P7" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q7" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="R7" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="S7" s="0" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>704</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="C8" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="0" t="s">
         <v>708</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="P8" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8" s="0" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="0" t="s">
         <v>712</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="C9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="O9" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="P9" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="R9" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="S9" s="0" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>719</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" s="0" t="s">
         <v>721</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="0" t="s">
         <v>722</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="0" t="s">
         <v>723</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="N10" s="0" t="s">
         <v>724</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="O10" s="0" t="s">
         <v>725</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="P10" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q10" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="R10" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="S10" s="0" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="0" t="s">
         <v>727</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="C11" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="0" t="s">
         <v>728</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L11" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="P11" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q11" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="R11" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="S11" s="0" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>734</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="0" t="s">
         <v>736</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="0" t="s">
         <v>701</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="0" t="s">
         <v>702</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="N12" s="0" t="s">
         <v>700</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="O12" s="0" t="s">
         <v>557</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="P12" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q12" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="R12" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="S12" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="T12" s="1" t="s">
+      <c r="T12" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="U12" s="1" t="s">
+      <c r="U12" s="0" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="0" t="s">
         <v>738</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="L13" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="O13" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="P13" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="R13" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="S13" s="0" t="s">
         <v>679</v>
       </c>
-      <c r="T13" s="1" t="s">
+      <c r="T13" s="0" t="s">
         <v>745</v>
       </c>
-      <c r="U13" s="1" t="s">
+      <c r="U13" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="V13" s="1" t="s">
+      <c r="V13" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="W13" s="1" t="s">
+      <c r="W13" s="0" t="s">
         <v>682</v>
       </c>
-      <c r="X13" s="1" t="s">
+      <c r="X13" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="Y13" s="1" t="s">
+      <c r="Y13" s="0" t="s">
         <v>746</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>747</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="L14" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="O14" s="0" t="s">
         <v>753</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="P14" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="R14" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="S14" s="0" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>755</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="0" t="s">
         <v>756</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="L15" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="O15" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="P15" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="0" t="s">
         <v>756</v>
       </c>
-      <c r="R15" s="1" t="s">
+      <c r="R15" s="0" t="s">
         <v>763</v>
       </c>
-      <c r="S15" s="1" t="s">
+      <c r="S15" s="0" t="s">
         <v>764</v>
       </c>
-      <c r="T15" s="1" t="s">
+      <c r="T15" s="0" t="s">
         <v>765</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="0" t="s">
         <v>766</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="0" t="s">
         <v>756</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="0" t="s">
         <v>768</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" s="0" t="s">
         <v>769</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" s="0" t="s">
         <v>770</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N16" s="0" t="s">
         <v>771</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="O16" s="0" t="s">
         <v>772</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="P16" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="0" t="s">
         <v>756</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="R16" s="0" t="s">
         <v>773</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="S16" s="0" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="0" t="s">
         <v>775</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="C17" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="L17" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="O17" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="P17" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="R17" s="0" t="s">
         <v>783</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="S17" s="0" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="0" t="s">
         <v>785</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="C18" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="L18" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="O18" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="Q18" s="1" t="s">
+      <c r="P18" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="R18" s="0" t="s">
         <v>783</v>
       </c>
-      <c r="S18" s="1" t="s">
+      <c r="S18" s="0" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="0" t="s">
         <v>792</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="C19" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="L19" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="O19" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="Q19" s="1" t="s">
+      <c r="P19" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="R19" s="0" t="s">
         <v>783</v>
       </c>
-      <c r="S19" s="1" t="s">
+      <c r="S19" s="0" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="0" t="s">
         <v>799</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="C20" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="L20" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="N20" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="O20" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="Q20" s="1" t="s">
+      <c r="P20" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="R20" s="0" t="s">
         <v>783</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="S20" s="0" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="0" t="s">
         <v>807</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="C21" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K21" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L21" s="3" t="s">
         <v>810</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="O21" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="Q21" s="1" t="s">
+      <c r="P21" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="R21" s="0" t="s">
         <v>783</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="S21" s="0" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="0" t="s">
         <v>814</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="C22" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="0" t="s">
         <v>815</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="0" t="s">
         <v>817</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="L22" s="0" t="s">
         <v>818</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="M22" s="0" t="s">
         <v>819</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="N22" s="0" t="s">
         <v>820</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="O22" s="0" t="s">
         <v>821</v>
       </c>
-      <c r="Q22" s="1" t="s">
+      <c r="P22" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="0" t="s">
         <v>815</v>
       </c>
-      <c r="R22" s="1" t="s">
+      <c r="R22" s="0" t="s">
         <v>822</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="S22" s="0" t="s">
         <v>823</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="0" t="s">
         <v>824</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="C23" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="L23" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="M23" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="N23" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="O23" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="P23" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="R23" s="1" t="s">
+      <c r="R23" s="0" t="s">
         <v>832</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="0" t="s">
         <v>833</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="L24" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="M24" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="N24" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="O24" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="Q24" s="1" t="s">
+      <c r="P24" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="R24" s="1" t="s">
+      <c r="R24" s="0" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="0" t="s">
         <v>841</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="C25" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="K25" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="L25" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="M25" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="N25" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="O25" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="Q25" s="1" t="s">
+      <c r="P25" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="R25" s="1" t="s">
+      <c r="R25" s="0" t="s">
         <v>848</v>
       </c>
-      <c r="S25" s="1" t="s">
+      <c r="S25" s="0" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="A26" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>850</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="C26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" s="0" t="s">
         <v>852</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="L26" s="0" t="s">
         <v>853</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="M26" s="0" t="s">
         <v>854</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="N26" s="0" t="s">
         <v>855</v>
       </c>
-      <c r="O26" s="1" t="s">
+      <c r="O26" s="0" t="s">
         <v>856</v>
       </c>
-      <c r="Q26" s="1" t="s">
+      <c r="P26" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="R26" s="1" t="s">
+      <c r="R26" s="0" t="s">
         <v>857</v>
       </c>
-      <c r="S26" s="1" t="s">
+      <c r="S26" s="0" t="s">
         <v>858</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="0" t="s">
         <v>859</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="C27" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" s="0" t="s">
         <v>862</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="L27" s="0" t="s">
         <v>863</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="M27" s="0" t="s">
         <v>864</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="N27" s="0" t="s">
         <v>865</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="O27" s="0" t="s">
         <v>866</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="P27" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="R27" s="0" t="s">
         <v>867</v>
       </c>
-      <c r="S27" s="1" t="s">
+      <c r="S27" s="0" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="0" t="s">
         <v>869</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="C28" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" s="0" t="s">
         <v>871</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="L28" s="0" t="s">
         <v>872</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="M28" s="0" t="s">
         <v>873</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="N28" s="0" t="s">
         <v>874</v>
       </c>
-      <c r="O28" s="1" t="s">
+      <c r="O28" s="0" t="s">
         <v>875</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="P28" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="R28" s="0" t="s">
         <v>876</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="0" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="0" t="s">
         <v>877</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="C29" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="K29" s="3" t="s">
         <v>879</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="L29" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="M29" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="N29" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="O29" s="0" t="s">
         <v>883</v>
       </c>
-      <c r="Q29" s="1" t="s">
+      <c r="P29" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="R29" s="0" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="0" t="s">
         <v>885</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="C30" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="J30" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="K30" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="L30" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="M30" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="N30" s="3" t="s">
         <v>890</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="O30" s="3" t="s">
         <v>891</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="P30" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="R30" s="1" t="s">
+      <c r="R30" s="0" t="s">
         <v>867</v>
       </c>
-      <c r="S30" s="1" t="s">
+      <c r="S30" s="0" t="s">
         <v>892</v>
       </c>
-      <c r="T30" s="1" t="s">
+      <c r="T30" s="0" t="s">
         <v>893</v>
       </c>
-      <c r="U30" s="1" t="s">
+      <c r="U30" s="0" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="0" t="s">
         <v>895</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="1" t="s">
+      <c r="C31" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" s="0" t="s">
         <v>897</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="L31" s="0" t="s">
         <v>898</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="M31" s="0" t="s">
         <v>899</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="N31" s="0" t="s">
         <v>900</v>
       </c>
-      <c r="O31" s="1" t="s">
+      <c r="O31" s="0" t="s">
         <v>901</v>
       </c>
-      <c r="Q31" s="1" t="s">
+      <c r="P31" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="R31" s="1" t="s">
+      <c r="R31" s="0" t="s">
         <v>902</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="0" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="0" t="s">
         <v>903</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="C32" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J32" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="K32" s="3" t="s">
         <v>905</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="L32" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="M32" s="3" t="s">
         <v>907</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="N32" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="O32" s="3" t="s">
         <v>909</v>
       </c>
-      <c r="Q32" s="1" t="s">
+      <c r="P32" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="R32" s="1" t="s">
+      <c r="R32" s="0" t="s">
         <v>910</v>
       </c>
-      <c r="S32" s="1" t="s">
+      <c r="S32" s="0" t="s">
         <v>911</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="0" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="0" t="s">
         <v>912</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="C33" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="3" t="s">
         <v>913</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="K33" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="L33" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M33" s="3" t="s">
         <v>916</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="N33" s="3" t="s">
         <v>917</v>
       </c>
-      <c r="O33" s="2" t="s">
+      <c r="O33" s="3" t="s">
         <v>918</v>
       </c>
-      <c r="Q33" s="1" t="s">
+      <c r="P33" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="R33" s="1" t="s">
+      <c r="R33" s="0" t="s">
         <v>249</v>
       </c>
-      <c r="S33" s="1" t="s">
+      <c r="S33" s="0" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="0" t="s">
         <v>919</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="C34" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J34" s="3" t="s">
         <v>920</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K34" s="3" t="s">
         <v>921</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="L34" s="3" t="s">
         <v>922</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="M34" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="N34" s="3" t="s">
         <v>924</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="O34" s="3" t="s">
         <v>925</v>
       </c>
-      <c r="Q34" s="1" t="s">
+      <c r="P34" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="R34" s="1" t="s">
+      <c r="R34" s="0" t="s">
         <v>926</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="0" t="s">
         <v>927</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="C35" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="J35" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K35" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="L35" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="N35" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="O35" s="2" t="s">
+      <c r="O35" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="Q35" s="1" t="s">
+      <c r="P35" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="R35" s="1" t="s">
+      <c r="R35" s="0" t="s">
         <v>934</v>
       </c>
-      <c r="S35" s="1" t="s">
+      <c r="S35" s="0" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="0" t="s">
         <v>936</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="C36" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="J36" s="3" t="s">
         <v>937</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="0" t="s">
         <v>938</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="L36" s="0" t="s">
         <v>939</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="M36" s="0" t="s">
         <v>940</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="N36" s="0" t="s">
         <v>941</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="O36" s="0" t="s">
         <v>942</v>
       </c>
-      <c r="Q36" s="1" t="s">
+      <c r="P36" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q36" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="R36" s="1" t="s">
+      <c r="R36" s="0" t="s">
         <v>943</v>
       </c>
-      <c r="S36" s="1" t="s">
+      <c r="S36" s="0" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="0" t="s">
         <v>945</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="C37" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="J37" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="K37" s="3" t="s">
         <v>947</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="L37" s="3" t="s">
         <v>948</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M37" s="3" t="s">
         <v>949</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="N37" s="3" t="s">
         <v>950</v>
       </c>
-      <c r="O37" s="2" t="s">
+      <c r="O37" s="3" t="s">
         <v>951</v>
       </c>
-      <c r="Q37" s="1" t="s">
+      <c r="P37" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q37" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="R37" s="1" t="s">
+      <c r="R37" s="0" t="s">
         <v>328</v>
       </c>
-      <c r="S37" s="1" t="s">
+      <c r="S37" s="0" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="0" t="s">
         <v>952</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="C38" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="J38" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="K38" s="3" t="s">
         <v>954</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="L38" s="3" t="s">
         <v>955</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="M38" s="3" t="s">
         <v>956</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="N38" s="3" t="s">
         <v>957</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="O38" s="3" t="s">
         <v>958</v>
       </c>
-      <c r="Q38" s="1" t="s">
+      <c r="P38" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q38" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="R38" s="1" t="s">
+      <c r="R38" s="0" t="s">
         <v>959</v>
       </c>
-      <c r="S38" s="1" t="s">
+      <c r="S38" s="0" t="s">
         <v>960</v>
       </c>
-      <c r="T38" s="1" t="s">
+      <c r="T38" s="0" t="s">
         <v>961</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="0" t="s">
         <v>962</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="C39" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="J39" s="3" t="s">
         <v>963</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" s="0" t="s">
         <v>964</v>
       </c>
-      <c r="L39" s="1" t="s">
+      <c r="L39" s="0" t="s">
         <v>702</v>
       </c>
-      <c r="M39" s="1" t="s">
+      <c r="M39" s="0" t="s">
         <v>965</v>
       </c>
-      <c r="N39" s="1" t="s">
+      <c r="N39" s="0" t="s">
         <v>701</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="O39" s="0" t="s">
         <v>966</v>
       </c>
-      <c r="Q39" s="1" t="s">
+      <c r="P39" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q39" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="R39" s="1" t="s">
+      <c r="R39" s="0" t="s">
         <v>967</v>
       </c>
-      <c r="S39" s="1" t="s">
+      <c r="S39" s="0" t="s">
         <v>968</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="0" t="s">
         <v>969</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="C40" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J40" s="2" t="s">
+      <c r="J40" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K40" s="0" t="s">
         <v>971</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="L40" s="0" t="s">
         <v>972</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="M40" s="0" t="s">
         <v>973</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="N40" s="0" t="s">
         <v>974</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="O40" s="0" t="s">
         <v>975</v>
       </c>
-      <c r="Q40" s="1" t="s">
+      <c r="P40" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q40" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="R40" s="1" t="s">
+      <c r="R40" s="0" t="s">
         <v>976</v>
       </c>
-      <c r="S40" s="1" t="s">
+      <c r="S40" s="0" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="0" t="s">
         <v>978</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="C41" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="J41" s="3" t="s">
         <v>979</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="K41" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="L41" s="3" t="s">
         <v>981</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="M41" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="N41" s="2" t="s">
+      <c r="N41" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="O41" s="2" t="s">
+      <c r="O41" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="Q41" s="1" t="s">
+      <c r="P41" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q41" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="R41" s="1" t="s">
+      <c r="R41" s="0" t="s">
         <v>985</v>
       </c>
-      <c r="S41" s="1" t="s">
+      <c r="S41" s="0" t="s">
         <v>986</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="0" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="0" t="s">
         <v>987</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42" s="1" t="s">
+      <c r="C42" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="J42" s="3" t="s">
         <v>988</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="K42" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="L42" s="2" t="s">
+      <c r="L42" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="M42" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="N42" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="O42" s="2" t="s">
+      <c r="O42" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="Q42" s="1" t="s">
+      <c r="P42" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q42" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="R42" s="1" t="s">
+      <c r="R42" s="0" t="s">
         <v>994</v>
       </c>
-      <c r="S42" s="1" t="s">
+      <c r="S42" s="0" t="s">
         <v>995</v>
       </c>
-      <c r="T42" s="1" t="s">
+      <c r="T42" s="0" t="s">
         <v>996</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="0" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="0" t="s">
         <v>997</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="1" t="s">
+      <c r="C43" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="J43" s="3" t="s">
         <v>998</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="K43" s="3" t="s">
         <v>999</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="L43" s="3" t="s">
         <v>1000</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="M43" s="3" t="s">
         <v>1001</v>
       </c>
-      <c r="N43" s="2" t="s">
+      <c r="N43" s="3" t="s">
         <v>1002</v>
       </c>
-      <c r="O43" s="2" t="s">
+      <c r="O43" s="3" t="s">
         <v>1003</v>
       </c>
-      <c r="Q43" s="1" t="s">
+      <c r="P43" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q43" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="R43" s="0" t="s">
         <v>1004</v>
       </c>
-      <c r="S43" s="1" t="s">
+      <c r="S43" s="0" t="s">
         <v>1005</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="0" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="0" t="s">
         <v>1006</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="C44" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J44" s="2" t="s">
+      <c r="J44" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="K44" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="L44" s="2" t="s">
+      <c r="L44" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="M44" s="3" t="s">
         <v>1010</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="N44" s="3" t="s">
         <v>1011</v>
       </c>
-      <c r="O44" s="2" t="s">
+      <c r="O44" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="Q44" s="1" t="s">
+      <c r="P44" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q44" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="R44" s="1" t="s">
+      <c r="R44" s="0" t="s">
         <v>1013</v>
       </c>
-      <c r="S44" s="1" t="s">
+      <c r="S44" s="0" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="0" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="0" t="s">
         <v>1014</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="C45" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="J45" s="3" t="s">
         <v>1015</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="K45" s="3" t="s">
         <v>1016</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="L45" s="3" t="s">
         <v>1017</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="M45" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="N45" s="2" t="s">
+      <c r="N45" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="O45" s="2" t="s">
+      <c r="O45" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="Q45" s="1" t="s">
+      <c r="P45" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q45" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="R45" s="1" t="s">
+      <c r="R45" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="S45" s="1" t="s">
+      <c r="S45" s="0" t="s">
         <v>1021</v>
       </c>
-      <c r="T45" s="1" t="s">
+      <c r="T45" s="0" t="s">
         <v>1022</v>
       </c>
-      <c r="U45" s="1" t="s">
+      <c r="U45" s="0" t="s">
         <v>1023</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="0" t="s">
         <v>1024</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="C46" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="J46" s="3" t="s">
         <v>1025</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="K46" s="3" t="s">
         <v>1026</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="L46" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="M46" s="3" t="s">
         <v>1028</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="N46" s="3" t="s">
         <v>1029</v>
       </c>
-      <c r="O46" s="2" t="s">
+      <c r="O46" s="3" t="s">
         <v>1030</v>
       </c>
-      <c r="Q46" s="1" t="s">
+      <c r="P46" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q46" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="R46" s="1" t="s">
+      <c r="R46" s="0" t="s">
         <v>1031</v>
       </c>
-      <c r="S46" s="1" t="s">
+      <c r="S46" s="0" t="s">
         <v>1032</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="0" t="s">
         <v>1033</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="C47" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="J47" s="3" t="s">
         <v>1034</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="K47" s="3" t="s">
         <v>1035</v>
       </c>
-      <c r="L47" s="2" t="s">
+      <c r="L47" s="3" t="s">
         <v>1036</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="M47" s="3" t="s">
         <v>1037</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="N47" s="3" t="s">
         <v>1038</v>
       </c>
-      <c r="O47" s="2" t="s">
+      <c r="O47" s="3" t="s">
         <v>1039</v>
       </c>
-      <c r="Q47" s="1" t="s">
+      <c r="P47" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q47" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="R47" s="1" t="s">
+      <c r="R47" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="S47" s="1" t="s">
+      <c r="S47" s="0" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="0" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="0" t="s">
         <v>1040</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="C48" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="J48" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K48" s="3" t="s">
         <v>1042</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="L48" s="3" t="s">
         <v>1043</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="M48" s="3" t="s">
         <v>1044</v>
       </c>
-      <c r="N48" s="2" t="s">
+      <c r="N48" s="3" t="s">
         <v>1045</v>
       </c>
-      <c r="O48" s="2" t="s">
+      <c r="O48" s="3" t="s">
         <v>1046</v>
       </c>
-      <c r="Q48" s="1" t="s">
+      <c r="P48" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q48" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="R48" s="1" t="s">
+      <c r="R48" s="0" t="s">
         <v>1047</v>
       </c>
-      <c r="S48" s="1" t="s">
+      <c r="S48" s="0" t="s">
         <v>1031</v>
       </c>
-      <c r="T48" s="1" t="s">
+      <c r="T48" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="U48" s="1" t="s">
+      <c r="U48" s="0" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="0" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="0" t="s">
         <v>1048</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49" s="1" t="s">
+      <c r="C49" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="J49" s="3" t="s">
         <v>1049</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="K49" s="3" t="s">
         <v>1050</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="L49" s="3" t="s">
         <v>1051</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="M49" s="3" t="s">
         <v>1052</v>
       </c>
-      <c r="N49" s="2" t="s">
+      <c r="N49" s="3" t="s">
         <v>1053</v>
       </c>
-      <c r="O49" s="2" t="s">
+      <c r="O49" s="3" t="s">
         <v>1054</v>
       </c>
-      <c r="Q49" s="1" t="s">
+      <c r="P49" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q49" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="R49" s="1" t="s">
+      <c r="R49" s="0" t="s">
         <v>1055</v>
       </c>
-      <c r="S49" s="1" t="s">
+      <c r="S49" s="0" t="s">
         <v>1056</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="0" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="0" t="s">
         <v>1057</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" s="1" t="s">
+      <c r="C50" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="J50" s="3" t="s">
         <v>1058</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="K50" s="3" t="s">
         <v>1059</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="L50" s="3" t="s">
         <v>1060</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="M50" s="3" t="s">
         <v>1061</v>
       </c>
-      <c r="N50" s="2" t="s">
+      <c r="N50" s="3" t="s">
         <v>1062</v>
       </c>
-      <c r="O50" s="2" t="s">
+      <c r="O50" s="3" t="s">
         <v>1063</v>
       </c>
-      <c r="Q50" s="1" t="s">
+      <c r="P50" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q50" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="R50" s="1" t="s">
+      <c r="R50" s="0" t="s">
         <v>480</v>
       </c>
-      <c r="S50" s="1" t="s">
+      <c r="S50" s="0" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="0" t="s">
         <v>1064</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" s="1" t="s">
+      <c r="C51" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="J51" s="3" t="s">
         <v>1065</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="K51" s="0" t="s">
         <v>1066</v>
       </c>
-      <c r="L51" s="1" t="s">
+      <c r="L51" s="0" t="s">
         <v>1067</v>
       </c>
-      <c r="M51" s="1" t="s">
+      <c r="M51" s="0" t="s">
         <v>702</v>
       </c>
-      <c r="N51" s="1" t="s">
+      <c r="N51" s="0" t="s">
         <v>965</v>
       </c>
-      <c r="O51" s="1" t="s">
+      <c r="O51" s="0" t="s">
         <v>966</v>
       </c>
-      <c r="Q51" s="1" t="s">
+      <c r="P51" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q51" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="R51" s="1" t="s">
+      <c r="R51" s="0" t="s">
         <v>1068</v>
       </c>
-      <c r="S51" s="1" t="s">
+      <c r="S51" s="0" t="s">
         <v>1069</v>
       </c>
-      <c r="T51" s="1" t="s">
+      <c r="T51" s="0" t="s">
         <v>1070</v>
       </c>
-      <c r="U51" s="1" t="s">
+      <c r="U51" s="0" t="s">
         <v>1071</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="0" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="0" t="s">
         <v>1072</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="C52" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H52" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J52" s="2" t="s">
+      <c r="J52" s="3" t="s">
         <v>1073</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="K52" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="L52" s="2" t="s">
+      <c r="L52" s="3" t="s">
         <v>1075</v>
       </c>
-      <c r="M52" s="2" t="s">
+      <c r="M52" s="3" t="s">
         <v>1076</v>
       </c>
-      <c r="N52" s="2" t="s">
+      <c r="N52" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="O52" s="2" t="s">
+      <c r="O52" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="Q52" s="1" t="s">
+      <c r="P52" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q52" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="R52" s="1" t="s">
+      <c r="R52" s="0" t="s">
         <v>1079</v>
       </c>
-      <c r="S52" s="1" t="s">
+      <c r="S52" s="0" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="0" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="0" t="s">
         <v>1080</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D53" s="1" t="s">
+      <c r="C53" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J53" s="2" t="s">
+      <c r="J53" s="3" t="s">
         <v>1081</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="K53" s="3" t="s">
         <v>1082</v>
       </c>
-      <c r="L53" s="2" t="s">
+      <c r="L53" s="3" t="s">
         <v>1083</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="M53" s="3" t="s">
         <v>1084</v>
       </c>
-      <c r="N53" s="2" t="s">
+      <c r="N53" s="3" t="s">
         <v>1085</v>
       </c>
-      <c r="O53" s="2" t="s">
+      <c r="O53" s="3" t="s">
         <v>1086</v>
       </c>
-      <c r="Q53" s="1" t="s">
+      <c r="P53" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q53" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="R53" s="1" t="s">
+      <c r="R53" s="0" t="s">
         <v>1087</v>
       </c>
-      <c r="S53" s="1" t="s">
+      <c r="S53" s="0" t="s">
         <v>1088</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="0" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="0" t="s">
         <v>1089</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D54" s="1" t="s">
+      <c r="C54" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H54" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J54" s="2" t="s">
+      <c r="J54" s="3" t="s">
         <v>1090</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="K54" s="3" t="s">
         <v>1091</v>
       </c>
-      <c r="L54" s="2" t="s">
+      <c r="L54" s="3" t="s">
         <v>1092</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="M54" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="N54" s="2" t="s">
+      <c r="N54" s="3" t="s">
         <v>1094</v>
       </c>
-      <c r="O54" s="2" t="s">
+      <c r="O54" s="3" t="s">
         <v>1095</v>
       </c>
-      <c r="Q54" s="1" t="s">
+      <c r="P54" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q54" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="R54" s="1" t="s">
+      <c r="R54" s="0" t="s">
         <v>1096</v>
       </c>
-      <c r="S54" s="1" t="s">
+      <c r="S54" s="0" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="0" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="0" t="s">
         <v>1097</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="C55" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J55" s="2" t="s">
+      <c r="J55" s="3" t="s">
         <v>1098</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="K55" s="3" t="s">
         <v>1099</v>
       </c>
-      <c r="L55" s="2" t="s">
+      <c r="L55" s="3" t="s">
         <v>1100</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="M55" s="3" t="s">
         <v>1101</v>
       </c>
-      <c r="N55" s="2" t="s">
+      <c r="N55" s="3" t="s">
         <v>1102</v>
       </c>
-      <c r="O55" s="2" t="s">
+      <c r="O55" s="3" t="s">
         <v>1103</v>
       </c>
-      <c r="Q55" s="1" t="s">
+      <c r="P55" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q55" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="R55" s="1" t="s">
+      <c r="R55" s="0" t="s">
         <v>397</v>
       </c>
-      <c r="S55" s="1" t="s">
+      <c r="S55" s="0" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="0" t="s">
         <v>1104</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D56" s="1" t="s">
+      <c r="C56" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="J56" s="3" t="s">
         <v>1105</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="K56" s="3" t="s">
         <v>1106</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="L56" s="3" t="s">
         <v>1107</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="M56" s="3" t="s">
         <v>1108</v>
       </c>
-      <c r="N56" s="2" t="s">
+      <c r="N56" s="3" t="s">
         <v>1109</v>
       </c>
-      <c r="O56" s="2" t="s">
+      <c r="O56" s="3" t="s">
         <v>1110</v>
       </c>
-      <c r="Q56" s="1" t="s">
+      <c r="P56" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q56" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="R56" s="1" t="s">
+      <c r="R56" s="0" t="s">
         <v>398</v>
       </c>
-      <c r="S56" s="1" t="s">
+      <c r="S56" s="0" t="s">
         <v>1111</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="0" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="0" t="s">
         <v>1112</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57" s="1" t="s">
+      <c r="C57" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="J57" s="3" t="s">
         <v>1113</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="K57" s="3" t="s">
         <v>1114</v>
       </c>
-      <c r="L57" s="2" t="s">
+      <c r="L57" s="3" t="s">
         <v>1115</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="M57" s="3" t="s">
         <v>1116</v>
       </c>
-      <c r="N57" s="2" t="s">
+      <c r="N57" s="3" t="s">
         <v>1117</v>
       </c>
-      <c r="O57" s="2" t="s">
+      <c r="O57" s="3" t="s">
         <v>1118</v>
       </c>
-      <c r="Q57" s="1" t="s">
+      <c r="P57" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q57" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="R57" s="1" t="s">
+      <c r="R57" s="0" t="s">
         <v>1119</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="0" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="0" t="s">
         <v>1120</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D58" s="1" t="s">
+      <c r="C58" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="H58" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J58" s="2" t="s">
+      <c r="J58" s="3" t="s">
         <v>1121</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="K58" s="3" t="s">
         <v>1122</v>
       </c>
-      <c r="L58" s="2" t="s">
+      <c r="L58" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="M58" s="3" t="s">
         <v>1124</v>
       </c>
-      <c r="N58" s="2" t="s">
+      <c r="N58" s="3" t="s">
         <v>1125</v>
       </c>
-      <c r="O58" s="2" t="s">
+      <c r="O58" s="3" t="s">
         <v>1126</v>
       </c>
-      <c r="Q58" s="1" t="s">
+      <c r="P58" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q58" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="R58" s="1" t="s">
+      <c r="R58" s="0" t="s">
         <v>1127</v>
       </c>
-      <c r="S58" s="1" t="s">
+      <c r="S58" s="0" t="s">
         <v>1128</v>
       </c>
-      <c r="T58" s="1" t="s">
+      <c r="T58" s="0" t="s">
         <v>1129</v>
       </c>
-      <c r="U58" s="1" t="s">
+      <c r="U58" s="0" t="s">
         <v>1130</v>
       </c>
-      <c r="V58" s="1" t="s">
+      <c r="V58" s="0" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="0" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="0" t="s">
         <v>1132</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D59" s="1" t="s">
+      <c r="C59" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="J59" s="3" t="s">
         <v>1133</v>
       </c>
-      <c r="K59" s="2" t="s">
+      <c r="K59" s="3" t="s">
         <v>1134</v>
       </c>
-      <c r="L59" s="2" t="s">
+      <c r="L59" s="3" t="s">
         <v>1135</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="M59" s="3" t="s">
         <v>1136</v>
       </c>
-      <c r="N59" s="2" t="s">
+      <c r="N59" s="3" t="s">
         <v>1137</v>
       </c>
-      <c r="O59" s="2" t="s">
+      <c r="O59" s="3" t="s">
         <v>1138</v>
       </c>
-      <c r="Q59" s="1" t="s">
+      <c r="P59" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q59" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="R59" s="1" t="s">
+      <c r="R59" s="0" t="s">
         <v>1127</v>
       </c>
-      <c r="S59" s="1" t="s">
+      <c r="S59" s="0" t="s">
         <v>1130</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="0" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="0" t="s">
         <v>1139</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D60" s="1" t="s">
+      <c r="C60" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="I60" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J60" s="2" t="s">
+      <c r="J60" s="3" t="s">
         <v>1140</v>
       </c>
-      <c r="K60" s="2" t="s">
+      <c r="K60" s="3" t="s">
         <v>1141</v>
       </c>
-      <c r="L60" s="2" t="s">
+      <c r="L60" s="3" t="s">
         <v>1142</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="M60" s="3" t="s">
         <v>1143</v>
       </c>
-      <c r="N60" s="2" t="s">
+      <c r="N60" s="3" t="s">
         <v>1144</v>
       </c>
-      <c r="O60" s="2" t="s">
+      <c r="O60" s="3" t="s">
         <v>1145</v>
       </c>
-      <c r="Q60" s="1" t="s">
+      <c r="P60" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q60" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="R60" s="1" t="s">
+      <c r="R60" s="0" t="s">
         <v>1127</v>
       </c>
-      <c r="S60" s="1" t="s">
+      <c r="S60" s="0" t="s">
         <v>1146</v>
       </c>
-      <c r="T60" s="1" t="s">
+      <c r="T60" s="0" t="s">
         <v>1147</v>
       </c>
-      <c r="U60" s="1" t="s">
+      <c r="U60" s="0" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="0" t="s">
         <v>1148</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D61" s="1" t="s">
+      <c r="C61" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="G61" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="I61" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="J61" s="2" t="s">
+      <c r="J61" s="3" t="s">
         <v>1149</v>
       </c>
-      <c r="K61" s="2" t="s">
+      <c r="K61" s="3" t="s">
         <v>1150</v>
       </c>
-      <c r="L61" s="2" t="s">
+      <c r="L61" s="3" t="s">
         <v>1151</v>
       </c>
-      <c r="M61" s="2" t="s">
+      <c r="M61" s="3" t="s">
         <v>1152</v>
       </c>
-      <c r="N61" s="2" t="s">
+      <c r="N61" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="O61" s="2" t="s">
+      <c r="O61" s="3" t="s">
         <v>1154</v>
       </c>
-      <c r="Q61" s="1" t="s">
+      <c r="P61" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q61" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="R61" s="1" t="s">
+      <c r="R61" s="0" t="s">
         <v>994</v>
       </c>
-      <c r="S61" s="1" t="s">
+      <c r="S61" s="0" t="s">
         <v>996</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -23073,7 +23256,9 @@
   <dimension ref="A1:U81"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="1" style="1" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="1" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="36.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="9" style="1" width="9.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
